--- a/AI_DecisionLogs.xlsx
+++ b/AI_DecisionLogs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="51">
   <si>
     <t>DecisionID</t>
   </si>
@@ -79,7 +79,28 @@
     <t>4b50e7bc-0cde-46a5-9ce2-23c0fd79a29b</t>
   </si>
   <si>
+    <t>e53e5d52-5de6-4d48-87ff-d878376683d2</t>
+  </si>
+  <si>
+    <t>41b6400c-5963-46a6-a0ca-d3f20792a2b1</t>
+  </si>
+  <si>
+    <t>a2130a20-316f-41e5-be53-a5e6d7fe23d3</t>
+  </si>
+  <si>
+    <t>3a76db80-695b-47fd-a87f-2a6244cc9aa8</t>
+  </si>
+  <si>
+    <t>e2b5e891-cc1e-4924-a337-ddd2426825bb</t>
+  </si>
+  <si>
+    <t>193233a9-deef-4c05-a443-307e29fcc290</t>
+  </si>
+  <si>
     <t>20260328_063053</t>
+  </si>
+  <si>
+    <t>20260513_044158</t>
   </si>
   <si>
     <t>FEEDBACK</t>
@@ -481,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38.7109375" customWidth="1"/>
@@ -495,7 +516,8 @@
     <col min="9" max="9" width="12.7109375" customWidth="1"/>
     <col min="10" max="10" width="9.7109375" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" customWidth="1"/>
-    <col min="12" max="13" width="12.7109375" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" customWidth="1"/>
+    <col min="13" max="13" width="nan" customWidth="1"/>
     <col min="14" max="14" width="15.7109375" customWidth="1"/>
     <col min="15" max="15" width="7.7109375" customWidth="1"/>
   </cols>
@@ -552,31 +574,31 @@
         <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C2" s="1">
         <v>46109</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G2" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L2" s="1">
         <v>46110</v>
@@ -587,31 +609,31 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1">
         <v>46109</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F3" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G3" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H3" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="I3" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L3" s="1">
         <v>46110</v>
@@ -622,31 +644,31 @@
         <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1">
         <v>46109</v>
       </c>
       <c r="D4" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G4" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H4" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I4" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L4" s="1">
         <v>46111</v>
@@ -657,31 +679,31 @@
         <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C5" s="1">
         <v>46109</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="F5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="I5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L5" s="1">
         <v>46111</v>
@@ -692,31 +714,31 @@
         <v>19</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1">
         <v>46109</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="H6" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L6" s="1">
         <v>46112</v>
@@ -727,34 +749,244 @@
         <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1">
         <v>46109</v>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F7" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H7" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="I7" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="J7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="L7" s="1">
         <v>46110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46155</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" t="s">
+        <v>43</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="1">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46155</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G9" t="s">
+        <v>43</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" t="s">
+        <v>50</v>
+      </c>
+      <c r="L9" s="1">
+        <v>46156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46155</v>
+      </c>
+      <c r="D10" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" t="s">
+        <v>34</v>
+      </c>
+      <c r="F10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" t="s">
+        <v>50</v>
+      </c>
+      <c r="L10" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46155</v>
+      </c>
+      <c r="D11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G11" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" t="s">
+        <v>46</v>
+      </c>
+      <c r="I11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11" s="1">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46155</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" t="s">
+        <v>41</v>
+      </c>
+      <c r="G12" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" t="s">
+        <v>47</v>
+      </c>
+      <c r="I12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" t="s">
+        <v>50</v>
+      </c>
+      <c r="L12" s="1">
+        <v>46158</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46155</v>
+      </c>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" t="s">
+        <v>42</v>
+      </c>
+      <c r="G13" t="s">
+        <v>43</v>
+      </c>
+      <c r="H13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I13" t="s">
+        <v>49</v>
+      </c>
+      <c r="J13" t="s">
+        <v>50</v>
+      </c>
+      <c r="L13" s="1">
+        <v>46156</v>
       </c>
     </row>
   </sheetData>
